--- a/03-Excel/A376/结果表-新书订购表.xlsx
+++ b/03-Excel/A376/结果表-新书订购表.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4170" yWindow="3570" windowWidth="8235" windowHeight="7350" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4180" yWindow="3580" windowWidth="10000" windowHeight="7360" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新书订购表" sheetId="1" state="visible" r:id="rId1"/>
@@ -67,13 +67,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="10"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -495,10 +492,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col width="30.875" customWidth="1" min="1" max="1"/>
+    <col width="30.83203125" customWidth="1" min="1" max="1"/>
     <col width="26.5" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -549,10 +546,6 @@
           <t>定价：99.8</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="163.5" customHeight="1">
-      <c r="A5" s="2" t="n"/>
-      <c r="B5" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
